--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jscott8\R Projects\lsip_dashboard\Data\3-2_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EF1EA43-A181-4023-B441-3C7796AC8001}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E79F000-3509-45F2-A178-B28243B787ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1820" yWindow="20" windowWidth="20660" windowHeight="14300" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
   <sheets>
     <sheet name="dataText" sheetId="1" r:id="rId1"/>
@@ -807,10 +807,10 @@
     <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data since October 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 and February 2026 data, and so some data has been suppressed in these months. Finally,  the entirety of the March 2026 data is currently supressed so is excluded from any three-month averages.</t>
   </si>
   <si>
-    <t>July 2026 data</t>
-  </si>
-  <si>
     <t>April 2025 - Mar 2026</t>
+  </si>
+  <si>
+    <t>August 2026 data</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1293,7 @@
         <v>152</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -1334,7 +1334,7 @@
         <v>154</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>22</v>
@@ -1375,7 +1375,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>22</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>22</v>
@@ -1457,7 +1457,7 @@
         <v>153</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>22</v>
@@ -1498,7 +1498,7 @@
         <v>156</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>22</v>
@@ -1539,7 +1539,7 @@
         <v>157</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>22</v>
@@ -1580,7 +1580,7 @@
         <v>158</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
@@ -1621,7 +1621,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>217</v>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jscott8\R Projects\lsip_dashboard\Data\3-2_dataText\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E79F000-3509-45F2-A178-B28243B787ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{6E79F000-3509-45F2-A178-B28243B787ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CC77C1D-A5E2-433B-B742-F316BB3F6D80}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="230">
   <si>
     <t>inactiveRate</t>
   </si>
@@ -811,6 +811,44 @@
   </si>
   <si>
     <t>August 2026 data</t>
+  </si>
+  <si>
+    <t>apprenticeships</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://explore-education-statistics.service.gov.uk/find-statistics/apprenticeships/2024-25'&gt;Individualised Learner Record&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>Apprenticeships in</t>
+  </si>
+  <si>
+    <t>are apprenticeship volumes changing</t>
+  </si>
+  <si>
+    <t>The number of apprenticeships in</t>
+  </si>
+  <si>
+    <t>Apprenticeships</t>
+  </si>
+  <si>
+    <t>share of apprenticeships</t>
+  </si>
+  <si>
+    <t>Apprenticeships are</t>
+  </si>
+  <si>
+    <t>Include all age apprenticeships.
+Apprenticeships are paid jobs that incorporate on-the-job and off-the-job training leading to nationally recognised qualifications.
+Achievements are the number of learners who successfully complete an individual aim in an academic year.</t>
+  </si>
+  <si>
+    <t>&lt;ol&gt;
+  &lt;li&gt;Total achievements is the count of learners that completed their qualification at any point during the stated academic period.&lt;/li&gt;
+ &lt;li&gt;Learners achieving more than one course will appear only once in the grand total.&lt;/li&gt;
+ &lt;li&gt;Years shown represent academic years.&lt;/li&gt;
+&lt;li&gt;Use caution when interpreting this data. A difference between subgroups does not necessarily imply any causality. There could be other contributing factors at work.&lt;/li&gt;
+&lt;li&gt;Figures for LSIP and CAs have been calculated from Local Authority District data to create a back series. There may be small differences to the published data for these geographies due to rounding errors.&lt;/li&gt;
+&lt;/ol&gt;</t>
   </si>
 </sst>
 </file>
@@ -903,7 +941,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -925,6 +963,17 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1239,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D33D53-EEC7-4B18-8C67-5F9034426AB5}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="25" style="6" customWidth="1"/>
@@ -2188,6 +2237,45 @@
         <v>149</v>
       </c>
       <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:13" ht="232.5" thickBot="1">
+      <c r="A25" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>227</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{6E79F000-3509-45F2-A178-B28243B787ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CC77C1D-A5E2-433B-B742-F316BB3F6D80}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{6E79F000-3509-45F2-A178-B28243B787ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55D7D6EA-0D99-4C14-BDFD-534B4183CB15}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="230">
   <si>
     <t>inactiveRate</t>
   </si>
@@ -941,7 +941,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -963,17 +963,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2239,41 +2228,43 @@
       <c r="G24" s="8"/>
     </row>
     <row r="25" spans="1:13" ht="232.5" thickBot="1">
-      <c r="A25" s="11" t="s">
+      <c r="A25" t="s">
         <v>220</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="11" t="s">
+      <c r="C25" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" t="s">
         <v>221</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="H25" s="15" t="s">
+      <c r="H25" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="I25" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="J25" s="15" t="s">
+      <c r="J25" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="K25" s="15" t="s">
+      <c r="K25" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="L25" s="15" t="s">
+      <c r="L25" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="M25" s="15" t="s">
+      <c r="M25" s="8" t="s">
         <v>227</v>
       </c>
     </row>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{6E79F000-3509-45F2-A178-B28243B787ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55D7D6EA-0D99-4C14-BDFD-534B4183CB15}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{6E79F000-3509-45F2-A178-B28243B787ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{321F2D72-C87A-468B-B94A-F5611A78C7CF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="229">
   <si>
     <t>inactiveRate</t>
   </si>
@@ -677,9 +677,6 @@
 &lt;/p&gt;</t>
   </si>
   <si>
-    <t>AY23/24 data</t>
-  </si>
-  <si>
     <t>AY22/23 data</t>
   </si>
   <si>
@@ -703,34 +700,12 @@
     <t>Mar 2025 data</t>
   </si>
   <si>
-    <t>Destination measures show the percentage of students going to or remaining in an education, apprenticeship or employment destination in the academic year after completing Key Stage 4 studies (usually aged between 14 to 16). The cohort of learners used in the metrics here completed in AY22/23.</t>
-  </si>
-  <si>
-    <t>Destination measures show the percentage of students going to or remaining in an education, apprenticeship or employment destination in the academic year after completing Key Stage 5 studies (usually aged 18). The cohort of learners used in the metrics here completed in AY22/23.</t>
-  </si>
-  <si>
     <t>&lt;ol&gt;
   &lt;li&gt;Data based on destinations of state-funded mainstream schools and colleges.&lt;/li&gt;
  &lt;li&gt;There is no double counting across destinations, a young person is reported in one destination category only.&lt;/li&gt;
  &lt;li&gt;If a student is registered as being in education and an apprenticeship, it is recorded as a sustained education and if a student is registered in employment along with an apprenticeship or in education, it is recorded as sustained employment.&lt;/li&gt;
 &lt;li&gt;Use caution when interpreting this data. A difference between subgroups does not necessarily imply any causality. There could be other contributing factors at work.&lt;/li&gt;
 &lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t>Destination measures show the percentage of students going to or remaining in an education, apprenticeship or employment destination in the academic year after completing Key Stage 4 studies (usually aged between 14 to 16). The cohort of learners used in the metrics here completed in AY22/23.
-A sustained destination is a count of young people recorded as having sustained participation (education and employment) for a 6 month period in the destination year.
-This means attending for all of the first two terms of the academic year (e.g. October 2023 to March 2024) at one or more education providers; spending 5 of the 6 months in employment or a combination of the two.
-A sustained apprenticeship is recorded when 6 months continuous participation is recorded at any point in the destination year (between August 2023 and July 2024).
-Not recorded includes pupils who were captured in the destination source data but who failed to meet the sustained participation criteria.
-Unknown (activity not captured): The student was not found to have any participation in education, apprenticeship or employment nor recorded as receiving out-of-work benefits at any point in the year. This also includes not being recorded by their Local Authority as NEET (not engaged in education, employment or training).</t>
-  </si>
-  <si>
-    <t>Destination measures show the percentage of students going to or remaining in an education, apprenticeship or employment destination in the academic year after completing Key Stage 5 studies (usually aged 18). The cohort of learners used in the metrics here completed in AY22/23.
-A sustained destination is a count of young people recorded as having sustained participation (education and employment) for a 6 month period in the destination year.
-This means attending for all of the first two terms of the academic year (e.g. October 2023 to March 2024) at one or more education providers; spending 5 of the 6 months in employment or a combination of the two.
-A sustained apprenticeship is recorded when 6 months continuous participation is recorded at any point in the destination year (between August 2023 and July 2024).
-Not recorded includes pupils who were captured in the destination source data but who failed to meet the sustained participation criteria.
-Unknown (activity not captured): The student was not found to have any participation in education, apprenticeship or employment nor recorded as receiving out-of-work benefits at any point in the year. This also includes not being recorded by their Local Authority as NEET (not engaged in education, employment or training).</t>
   </si>
   <si>
     <t>Dec 2023 - Dec 2024 data</t>
@@ -849,6 +824,28 @@
 &lt;li&gt;Use caution when interpreting this data. A difference between subgroups does not necessarily imply any causality. There could be other contributing factors at work.&lt;/li&gt;
 &lt;li&gt;Figures for LSIP and CAs have been calculated from Local Authority District data to create a back series. There may be small differences to the published data for these geographies due to rounding errors.&lt;/li&gt;
 &lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t>Destination measures show the percentage of students going to or remaining in an education, apprenticeship or employment destination in the academic year after completing Key Stage 4 studies (usually aged between 14 to 16). The cohort of learners used in the metrics here completed in AY23/24.</t>
+  </si>
+  <si>
+    <t>Destination measures show the percentage of students going to or remaining in an education, apprenticeship or employment destination in the academic year after completing Key Stage 5 studies (usually aged 18). The cohort of learners used in the metrics here completed in AY23/24.</t>
+  </si>
+  <si>
+    <t>Destination measures show the percentage of students going to or remaining in an education, apprenticeship or employment destination in the academic year after completing Key Stage 4 studies (usually aged between 14 to 16). The cohort of learners used in the metrics here completed in AY23/24.
+A sustained destination is a count of young people recorded as having sustained participation (education and employment) for a 6 month period in the destination year.
+This means attending for all of the first two terms of the academic year (e.g. October 2024 to March 2025) at one or more education providers; spending 5 of the 6 months in employment or a combination of the two.
+A sustained apprenticeship is recorded when 6 months continuous participation is recorded at any point in the destination year (between August 2024 and July 2025).
+Not recorded includes pupils who were captured in the destination source data but who failed to meet the sustained participation criteria.
+Unknown (activity not captured): The student was not found to have any participation in education, apprenticeship or employment nor recorded as receiving out-of-work benefits at any point in the year. This also includes not being recorded by their Local Authority as NEET (not engaged in education, employment or training).</t>
+  </si>
+  <si>
+    <t>Destination measures show the percentage of students going to or remaining in an education, apprenticeship or employment destination in the academic year after completing Key Stage 5 studies (usually aged 18). The cohort of learners used in the metrics here completed in AY23/24.
+A sustained destination is a count of young people recorded as having sustained participation (education and employment) for a 6 month period in the destination year.
+This means attending for all of the first two terms of the academic year (e.g. October 2024 to March 2025) at one or more education providers; spending 5 of the 6 months in employment or a combination of the two.
+A sustained apprenticeship is recorded when 6 months continuous participation is recorded at any point in the destination year (between August 2024 and July 2025).
+Not recorded includes pupils who were captured in the destination source data but who failed to meet the sustained participation criteria.
+Unknown (activity not captured): The student was not found to have any participation in education, apprenticeship or employment nor recorded as receiving out-of-work benefits at any point in the year. This also includes not being recorded by their Local Authority as NEET (not engaged in education, employment or training).</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1328,7 @@
         <v>152</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -1372,7 +1369,7 @@
         <v>154</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>22</v>
@@ -1413,7 +1410,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>22</v>
@@ -1454,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>22</v>
@@ -1495,7 +1492,7 @@
         <v>153</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>22</v>
@@ -1536,7 +1533,7 @@
         <v>156</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>22</v>
@@ -1577,7 +1574,7 @@
         <v>157</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>22</v>
@@ -1618,7 +1615,7 @@
         <v>158</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
@@ -1659,10 +1656,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>167</v>
@@ -1671,7 +1668,7 @@
         <v>22</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>35</v>
@@ -1700,7 +1697,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>23</v>
@@ -1741,7 +1738,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>23</v>
@@ -1782,7 +1779,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>23</v>
@@ -1823,19 +1820,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" t="s">
         <v>204</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="D14" t="s">
-        <v>209</v>
-      </c>
       <c r="E14" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>39</v>
@@ -1864,19 +1861,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="E15" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D15" t="s">
-        <v>209</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>40</v>
@@ -1905,19 +1902,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D16" t="s">
         <v>204</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" t="s">
-        <v>209</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>41</v>
@@ -1946,19 +1943,19 @@
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" t="s">
         <v>204</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D17" t="s">
-        <v>209</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>42</v>
@@ -1987,7 +1984,7 @@
         <v>160</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C18" t="s">
         <v>175</v>
@@ -2028,7 +2025,7 @@
         <v>168</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C19" t="s">
         <v>175</v>
@@ -2069,16 +2066,16 @@
         <v>12</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>150</v>
@@ -2110,19 +2107,19 @@
         <v>13</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C21" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>45</v>
@@ -2151,7 +2148,7 @@
         <v>159</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -2175,7 +2172,7 @@
         <v>64</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>125</v>
@@ -2190,13 +2187,13 @@
         <v>8</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>18</v>
@@ -2211,13 +2208,13 @@
         <v>11</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>18</v>
@@ -2229,43 +2226,43 @@
     </row>
     <row r="25" spans="1:13" ht="232.5" thickBot="1">
       <c r="A25" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D25" t="s">
+        <v>216</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="G25" s="8" t="s">
+      <c r="M25" s="8" t="s">
         <v>222</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jscott8\R Projects\lsip_dashboard\Data\3-2_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{6E79F000-3509-45F2-A178-B28243B787ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{321F2D72-C87A-468B-B94A-F5611A78C7CF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A40B41D-FC59-47BA-91C4-47EAE6F59AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
+    <workbookView xWindow="1530" yWindow="10690" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
   <sheets>
     <sheet name="dataText" sheetId="1" r:id="rId1"/>
@@ -697,9 +697,6 @@
     <t>Growth from 2024 to 2035. The LSIP boundaries have changed and new CAs have been created since this data was published so some areas no longer have data</t>
   </si>
   <si>
-    <t>Mar 2025 data</t>
-  </si>
-  <si>
     <t>&lt;ol&gt;
   &lt;li&gt;Data based on destinations of state-funded mainstream schools and colleges.&lt;/li&gt;
  &lt;li&gt;There is no double counting across destinations, a young person is reported in one destination category only.&lt;/li&gt;
@@ -846,6 +843,9 @@
 A sustained apprenticeship is recorded when 6 months continuous participation is recorded at any point in the destination year (between August 2024 and July 2025).
 Not recorded includes pupils who were captured in the destination source data but who failed to meet the sustained participation criteria.
 Unknown (activity not captured): The student was not found to have any participation in education, apprenticeship or employment nor recorded as receiving out-of-work benefits at any point in the year. This also includes not being recorded by their Local Authority as NEET (not engaged in education, employment or training).</t>
+  </si>
+  <si>
+    <t>Mar 2026 data</t>
   </si>
 </sst>
 </file>
@@ -1275,14 +1275,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D33D53-EEC7-4B18-8C67-5F9034426AB5}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="25" style="6" customWidth="1"/>
-    <col min="5" max="5" width="32.08984375" customWidth="1"/>
-    <col min="6" max="6" width="51.26953125" customWidth="1"/>
+    <col min="5" max="5" width="32.140625" customWidth="1"/>
+    <col min="6" max="6" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" thickBot="1">
+    <row r="1" spans="1:13" ht="15.75" thickBot="1">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>152</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -1369,7 +1369,7 @@
         <v>154</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>22</v>
@@ -1410,7 +1410,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>22</v>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>22</v>
@@ -1492,7 +1492,7 @@
         <v>153</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>22</v>
@@ -1533,7 +1533,7 @@
         <v>156</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>22</v>
@@ -1574,7 +1574,7 @@
         <v>157</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>22</v>
@@ -1615,7 +1615,7 @@
         <v>158</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
@@ -1651,15 +1651,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="218" thickBot="1">
+    <row r="10" spans="1:13" ht="255.75" thickBot="1">
       <c r="A10" t="s">
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>167</v>
@@ -1692,12 +1692,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="145.5" thickBot="1">
+    <row r="11" spans="1:13" ht="150.75" thickBot="1">
       <c r="A11" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>23</v>
@@ -1733,12 +1733,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="319.5" thickBot="1">
+    <row r="12" spans="1:13" ht="345.75" thickBot="1">
       <c r="A12" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>23</v>
@@ -1774,12 +1774,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="319.5" thickBot="1">
+    <row r="13" spans="1:13" ht="345.75" thickBot="1">
       <c r="A13" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>23</v>
@@ -1815,24 +1815,24 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="334" thickBot="1">
+    <row r="14" spans="1:13" ht="375.75" thickBot="1">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" t="s">
+        <v>203</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D14" t="s">
-        <v>204</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>39</v>
@@ -1856,24 +1856,24 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="319.5" thickBot="1">
+    <row r="15" spans="1:13" ht="360.75" thickBot="1">
       <c r="A15" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>200</v>
-      </c>
       <c r="D15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>40</v>
@@ -1902,19 +1902,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>41</v>
@@ -1943,19 +1943,19 @@
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D17" t="s">
         <v>203</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>42</v>
@@ -1979,12 +1979,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="290.5" thickBot="1">
+    <row r="18" spans="1:13" ht="300.75" thickBot="1">
       <c r="A18" t="s">
         <v>160</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C18" t="s">
         <v>175</v>
@@ -2020,12 +2020,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="290.5" thickBot="1">
+    <row r="19" spans="1:13" ht="300.75" thickBot="1">
       <c r="A19" t="s">
         <v>168</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C19" t="s">
         <v>175</v>
@@ -2061,21 +2061,21 @@
         <v>174</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="263" thickBot="1">
+    <row r="20" spans="1:13" ht="272.25" thickBot="1">
       <c r="A20" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>150</v>
@@ -2102,24 +2102,24 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="254" thickBot="1">
+    <row r="21" spans="1:13" ht="263.25" thickBot="1">
       <c r="A21" t="s">
         <v>13</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>192</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>45</v>
@@ -2143,7 +2143,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="334" thickBot="1">
+    <row r="22" spans="1:13" ht="375.75" thickBot="1">
       <c r="A22" t="s">
         <v>159</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>18</v>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="1:13" ht="363" thickBot="1">
+    <row r="24" spans="1:13" ht="405.75" thickBot="1">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>18</v>
@@ -2224,45 +2224,45 @@
       </c>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:13" ht="232.5" thickBot="1">
+    <row r="25" spans="1:13" ht="240.75" thickBot="1">
       <c r="A25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D25" t="s">
+        <v>215</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G25" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G25" s="8" t="s">
+      <c r="H25" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="I25" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="J25" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="K25" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="K25" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="L25" s="8" t="s">
+      <c r="M25" s="8" t="s">
         <v>221</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jscott8\R Projects\lsip_dashboard\Data\3-2_dataText\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A40B41D-FC59-47BA-91C4-47EAE6F59AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{1A40B41D-FC59-47BA-91C4-47EAE6F59AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA96CEFA-6828-48E1-A496-113F9AB70276}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="10690" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
   <sheets>
     <sheet name="dataText" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="240">
   <si>
     <t>inactiveRate</t>
   </si>
@@ -846,6 +846,39 @@
   </si>
   <si>
     <t>Mar 2026 data</t>
+  </si>
+  <si>
+    <t>neet_percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The NEET/not known rate in </t>
+  </si>
+  <si>
+    <t>are NEET/not known rates changing</t>
+  </si>
+  <si>
+    <t>NEET/not known rate</t>
+  </si>
+  <si>
+    <t>NEET/not known</t>
+  </si>
+  <si>
+    <t>The NEET/not known rate is</t>
+  </si>
+  <si>
+    <t>March 2026 data</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://explore-education-statistics.service.gov.uk/find-statistics/participation-in-education-training-and-neet-age-16-to-17-by-local-authority/2025-26'&gt;Participation in education, training and NEET age 16 to 17 by local authority&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This data is showing an estimate of the proportion of 16 and 17 year-olds  Not in Education or activity not known. Data is collected using the National Client Caseload Information System (NCCIS), which draws together local databases used to support young people to engage in education and training and plan services that meet young people’s needs. </t>
+  </si>
+  <si>
+    <t>NEET data is published at a Unitary Authority level, which is above the Local Authority District level shown in the maps and filters here. Therefore you will see missing data at the Local Authortity level in a number of places.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These figures are estimates based on management information. Reported figures may be inaccurate due to local authority organisational changes or processing issues, resulting in missing or incorrect activity data for some young people. There is considerable variation at local authority level in how well 16 and 17 year olds are tracked, and hence ‘activity not known’ proportions can impact on the estimates of the proportion NEET. </t>
   </si>
 </sst>
 </file>
@@ -1274,15 +1307,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D33D53-EEC7-4B18-8C67-5F9034426AB5}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:M26"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="25" style="6" customWidth="1"/>
-    <col min="5" max="5" width="32.140625" customWidth="1"/>
-    <col min="6" max="6" width="51.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.1796875" customWidth="1"/>
+    <col min="6" max="6" width="51.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1">
+    <row r="1" spans="1:13" ht="15" thickBot="1">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1651,7 +1684,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="255.75" thickBot="1">
+    <row r="10" spans="1:13" ht="218" thickBot="1">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1692,7 +1725,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="150.75" thickBot="1">
+    <row r="11" spans="1:13" ht="145.5" thickBot="1">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1733,7 +1766,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="345.75" thickBot="1">
+    <row r="12" spans="1:13" ht="319.5" thickBot="1">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1774,7 +1807,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="345.75" thickBot="1">
+    <row r="13" spans="1:13" ht="319.5" thickBot="1">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1815,7 +1848,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="375.75" thickBot="1">
+    <row r="14" spans="1:13" ht="334" thickBot="1">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1856,7 +1889,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="360.75" thickBot="1">
+    <row r="15" spans="1:13" ht="319.5" thickBot="1">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1979,7 +2012,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="300.75" thickBot="1">
+    <row r="18" spans="1:13" ht="290.5" thickBot="1">
       <c r="A18" t="s">
         <v>160</v>
       </c>
@@ -2020,7 +2053,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="300.75" thickBot="1">
+    <row r="19" spans="1:13" ht="290.5" thickBot="1">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -2061,7 +2094,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="272.25" thickBot="1">
+    <row r="20" spans="1:13" ht="263" thickBot="1">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -2102,7 +2135,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="263.25" thickBot="1">
+    <row r="21" spans="1:13" ht="254" thickBot="1">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -2143,7 +2176,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="375.75" thickBot="1">
+    <row r="22" spans="1:13" ht="334" thickBot="1">
       <c r="A22" t="s">
         <v>159</v>
       </c>
@@ -2203,7 +2236,7 @@
       </c>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="1:13" ht="405.75" thickBot="1">
+    <row r="24" spans="1:13" ht="363" thickBot="1">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2224,7 +2257,7 @@
       </c>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:13" ht="240.75" thickBot="1">
+    <row r="25" spans="1:13" ht="232.5" thickBot="1">
       <c r="A25" t="s">
         <v>214</v>
       </c>
@@ -2263,6 +2296,47 @@
       </c>
       <c r="M25" s="8" t="s">
         <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="160" thickBot="1">
+      <c r="A26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C26" t="s">
+        <v>238</v>
+      </c>
+      <c r="D26" t="s">
+        <v>236</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{1A40B41D-FC59-47BA-91C4-47EAE6F59AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA96CEFA-6828-48E1-A496-113F9AB70276}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{1A40B41D-FC59-47BA-91C4-47EAE6F59AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F004C54-FBEF-49B4-A84E-0EFE308D7650}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">This data is showing an estimate of the proportion of 16 and 17 year-olds  Not in Education or activity not known. Data is collected using the National Client Caseload Information System (NCCIS), which draws together local databases used to support young people to engage in education and training and plan services that meet young people’s needs. </t>
   </si>
   <si>
-    <t>NEET data is published at a Unitary Authority level, which is above the Local Authority District level shown in the maps and filters here. Therefore you will see missing data at the Local Authortity level in a number of places.</t>
-  </si>
-  <si>
     <t xml:space="preserve">These figures are estimates based on management information. Reported figures may be inaccurate due to local authority organisational changes or processing issues, resulting in missing or incorrect activity data for some young people. There is considerable variation at local authority level in how well 16 and 17 year olds are tracked, and hence ‘activity not known’ proportions can impact on the estimates of the proportion NEET. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEET/not known rates are shown here. Caution should be applied when using these figures due to the estimates being based on management information.  There is considerable variation in how well 16 and 17 year olds are tracked at local authority level. NEET data is published at a Unitary Authority level, which is above the Local Authority District level shown in the maps and filters here. Therefore you will see missing data at the Local Authortity level in a number of places. </t>
   </si>
 </sst>
 </file>
@@ -2306,7 +2306,7 @@
         <v>235</v>
       </c>
       <c r="C26" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D26" t="s">
         <v>236</v>
@@ -2315,7 +2315,7 @@
         <v>237</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>230</v>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jscott8\R Projects\lsip_dashboard\Data\3-2_dataText\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A40B41D-FC59-47BA-91C4-47EAE6F59AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{1A40B41D-FC59-47BA-91C4-47EAE6F59AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFDBD311-4DCE-4273-9D10-6CF14B75513C}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="10690" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
   <sheets>
     <sheet name="dataText" sheetId="1" r:id="rId1"/>
@@ -782,9 +782,6 @@
     <t>April 2025 - Mar 2026</t>
   </si>
   <si>
-    <t>August 2026 data</t>
-  </si>
-  <si>
     <t>apprenticeships</t>
   </si>
   <si>
@@ -846,6 +843,9 @@
   </si>
   <si>
     <t>Mar 2026 data</t>
+  </si>
+  <si>
+    <t>Sept 2026 data</t>
   </si>
 </sst>
 </file>
@@ -1275,14 +1275,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D33D53-EEC7-4B18-8C67-5F9034426AB5}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="25" style="6" customWidth="1"/>
-    <col min="5" max="5" width="32.140625" customWidth="1"/>
-    <col min="6" max="6" width="51.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.1796875" customWidth="1"/>
+    <col min="6" max="6" width="51.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1">
+    <row r="1" spans="1:13" ht="15" thickBot="1">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1651,12 +1651,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="255.75" thickBot="1">
+    <row r="10" spans="1:13" ht="218" thickBot="1">
       <c r="A10" t="s">
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>211</v>
@@ -1692,12 +1692,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="150.75" thickBot="1">
+    <row r="11" spans="1:13" ht="145.5" thickBot="1">
       <c r="A11" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>23</v>
@@ -1733,7 +1733,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="345.75" thickBot="1">
+    <row r="12" spans="1:13" ht="319.5" thickBot="1">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="345.75" thickBot="1">
+    <row r="13" spans="1:13" ht="319.5" thickBot="1">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="375.75" thickBot="1">
+    <row r="14" spans="1:13" ht="334" thickBot="1">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="360.75" thickBot="1">
+    <row r="15" spans="1:13" ht="319.5" thickBot="1">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="300.75" thickBot="1">
+    <row r="18" spans="1:13" ht="290.5" thickBot="1">
       <c r="A18" t="s">
         <v>160</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="300.75" thickBot="1">
+    <row r="19" spans="1:13" ht="290.5" thickBot="1">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="272.25" thickBot="1">
+    <row r="20" spans="1:13" ht="263" thickBot="1">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -2069,13 +2069,13 @@
         <v>198</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>208</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>150</v>
@@ -2102,7 +2102,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="263.25" thickBot="1">
+    <row r="21" spans="1:13" ht="254" thickBot="1">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -2110,13 +2110,13 @@
         <v>198</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>192</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>196</v>
@@ -2143,7 +2143,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="375.75" thickBot="1">
+    <row r="22" spans="1:13" ht="334" thickBot="1">
       <c r="A22" t="s">
         <v>159</v>
       </c>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="1:13" ht="405.75" thickBot="1">
+    <row r="24" spans="1:13" ht="363" thickBot="1">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2224,9 +2224,9 @@
       </c>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:13" ht="240.75" thickBot="1">
+    <row r="25" spans="1:13" ht="232.5" thickBot="1">
       <c r="A25" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>198</v>
@@ -2235,34 +2235,34 @@
         <v>22</v>
       </c>
       <c r="D25" t="s">
+        <v>214</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G25" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="G25" s="8" t="s">
+      <c r="H25" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="I25" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="J25" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="K25" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="K25" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="L25" s="8" t="s">
+      <c r="M25" s="8" t="s">
         <v>220</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{1A40B41D-FC59-47BA-91C4-47EAE6F59AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE238A2E-0641-45C4-B453-F6906972D6AA}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{1A40B41D-FC59-47BA-91C4-47EAE6F59AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FAF2E69-65D9-4AD2-8C5A-5369CF5589EF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -869,16 +869,19 @@
     <t>&lt;a href='https://explore-education-statistics.service.gov.uk/find-statistics/participation-in-education-training-and-neet-age-16-to-17-by-local-authority/2025-26'&gt;Participation in education, training and NEET age 16 to 17 by local authority&lt;/a&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">This data is showing an estimate of the proportion of 16 and 17 year-olds  Not in Education or activity not known. Data is collected using the National Client Caseload Information System (NCCIS), which draws together local databases used to support young people to engage in education and training and plan services that meet young people’s needs. </t>
-  </si>
-  <si>
     <t xml:space="preserve">These figures are estimates based on management information. Reported figures may be inaccurate due to local authority organisational changes or processing issues, resulting in missing or incorrect activity data for some young people. There is considerable variation at local authority level in how well 16 and 17 year olds are tracked, and hence ‘activity not known’ proportions can impact on the estimates of the proportion NEET. </t>
   </si>
   <si>
-    <t xml:space="preserve">NEET/not known rates are shown here. Caution should be applied when using these figures due to the estimates being based on management information.  There is considerable variation in how well 16 and 17 year olds are tracked at local authority level. NEET data is published at a Unitary Authority level, which is above the Local Authority District level shown in the maps and filters here. Therefore you will see missing data at the Local Authortity level in a number of places. </t>
-  </si>
-  <si>
     <t>Sept 2026 data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in education or training (NEET)/not known rates are shown here. Caution should be applied when using these figures due to the estimates being based on management information.  There is considerable variation in how well 16 and 17 year olds are tracked at local authority level. NEET data is published at a Unitary Authority level, which is above the Local Authority District level shown in the maps and filters here. Therefore you will see missing data at the Local Authortity level in a number of places. </t>
+  </si>
+  <si>
+    <t>&lt;ol&gt;
+  &lt;li&gt;This data is showing an estimate of the proportion of 16 and 17 year-olds  NEET or activity not known. Data is collected using the National Client Caseload Information System (NCCIS), which draws together local databases used to support young people to engage in education and training and plan services that meet young people’s needs. &lt;/li&gt;
+&lt;li&gt; Although the source used is the best source for local level NEET data, there are other sources of NEET data. For example the &lt;a href='https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief/2025'&gt;national reporting that cover 16-24 year olds&lt;/a&gt;. &lt;/li&gt;
+&lt;/ol&gt;</t>
   </si>
 </sst>
 </file>
@@ -1689,7 +1692,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>211</v>
@@ -2298,7 +2301,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="160" thickBot="1">
+    <row r="26" spans="1:13" ht="305" thickBot="1">
       <c r="A26" t="s">
         <v>228</v>
       </c>
@@ -2312,10 +2315,10 @@
         <v>235</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>229</v>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jscott8\R Projects\lsip_dashboard\Data\3-2_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{1A40B41D-FC59-47BA-91C4-47EAE6F59AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FAF2E69-65D9-4AD2-8C5A-5369CF5589EF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82889E7D-ABD8-4D1C-9844-F0B9922BF0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
   <sheets>
     <sheet name="dataText" sheetId="1" r:id="rId1"/>
@@ -875,13 +875,13 @@
     <t>Sept 2026 data</t>
   </si>
   <si>
-    <t xml:space="preserve">Not in education or training (NEET)/not known rates are shown here. Caution should be applied when using these figures due to the estimates being based on management information.  There is considerable variation in how well 16 and 17 year olds are tracked at local authority level. NEET data is published at a Unitary Authority level, which is above the Local Authority District level shown in the maps and filters here. Therefore you will see missing data at the Local Authortity level in a number of places. </t>
-  </si>
-  <si>
     <t>&lt;ol&gt;
   &lt;li&gt;This data is showing an estimate of the proportion of 16 and 17 year-olds  NEET or activity not known. Data is collected using the National Client Caseload Information System (NCCIS), which draws together local databases used to support young people to engage in education and training and plan services that meet young people’s needs. &lt;/li&gt;
-&lt;li&gt; Although the source used is the best source for local level NEET data, there are other sources of NEET data. For example the &lt;a href='https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief/2025'&gt;national reporting that cover 16-24 year olds&lt;/a&gt;. &lt;/li&gt;
+&lt;li&gt; Although the source used is the best source for local level NEET data, there are other sources of NEET data. For example the &lt;a href='https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief/2025'&gt;national reporting that covers 16-24 year olds&lt;/a&gt;. &lt;/li&gt;
 &lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in education or training (NEET)/not known rates are shown here. Caution should be applied when using these figures due to the estimates being based on management information. There is considerable variation in how well 16 and 17 year olds are tracked at local authority level. NEET data is published at a Unitary Authority level, which is above the Local Authority District level shown in the maps and filters here. Therefore you will see missing data at the Local Authortity level in a number of places. </t>
   </si>
 </sst>
 </file>
@@ -1311,11 +1311,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D33D53-EEC7-4B18-8C67-5F9034426AB5}">
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="25" style="6" customWidth="1"/>
-    <col min="5" max="5" width="32.1796875" customWidth="1"/>
-    <col min="6" max="6" width="51.26953125" customWidth="1"/>
+    <col min="5" max="5" width="32.21875" customWidth="1"/>
+    <col min="6" max="6" width="51.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" thickBot="1">
@@ -1687,7 +1687,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="218" thickBot="1">
+    <row r="10" spans="1:13" ht="202.2" thickBot="1">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="145.5" thickBot="1">
+    <row r="11" spans="1:13" ht="130.19999999999999" thickBot="1">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="319.5" thickBot="1">
+    <row r="12" spans="1:13" ht="303" thickBot="1">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="319.5" thickBot="1">
+    <row r="13" spans="1:13" ht="303" thickBot="1">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="334" thickBot="1">
+    <row r="14" spans="1:13" ht="303" thickBot="1">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="319.5" thickBot="1">
+    <row r="15" spans="1:13" ht="303" thickBot="1">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="290.5" thickBot="1">
+    <row r="18" spans="1:13" ht="274.2" thickBot="1">
       <c r="A18" t="s">
         <v>160</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="290.5" thickBot="1">
+    <row r="19" spans="1:13" ht="259.8" thickBot="1">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="263" thickBot="1">
+    <row r="20" spans="1:13" ht="289.8" thickBot="1">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="254" thickBot="1">
+    <row r="21" spans="1:13" ht="280.2" thickBot="1">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="334" thickBot="1">
+    <row r="22" spans="1:13" ht="303" thickBot="1">
       <c r="A22" t="s">
         <v>159</v>
       </c>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="1:13" ht="363" thickBot="1">
+    <row r="24" spans="1:13" ht="331.8" thickBot="1">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:13" ht="232.5" thickBot="1">
+    <row r="25" spans="1:13" ht="216.6" thickBot="1">
       <c r="A25" t="s">
         <v>213</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="305" thickBot="1">
+    <row r="26" spans="1:13" ht="303" thickBot="1">
       <c r="A26" t="s">
         <v>228</v>
       </c>
@@ -2309,13 +2309,13 @@
         <v>234</v>
       </c>
       <c r="C26" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D26" t="s">
         <v>235</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>236</v>
